--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\foler\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35892F0-76F8-422F-A1C1-56EC49A99AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71ADBF9-A241-431A-B281-3D175479358F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -523,6 +523,28 @@
     <t>カード4種</t>
     <rPh sb="4" eb="5">
       <t>シュ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26（一人当たり）</t>
+    <rPh sb="3" eb="6">
+      <t>ヒトリア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>36(カードUI周りはベータ)</t>
+    <rPh sb="8" eb="9">
+      <t>マワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1076,7 +1098,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -1086,7 +1108,9 @@
         <v>4</v>
       </c>
       <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="C3" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
     </row>
@@ -1095,7 +1119,9 @@
         <v>5</v>
       </c>
       <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
+      <c r="C4" s="8">
+        <v>1</v>
+      </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
     </row>
@@ -1104,7 +1130,9 @@
         <v>6</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
     </row>
@@ -1116,7 +1144,7 @@
         <v>42</v>
       </c>
       <c r="C6" s="13">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -1136,7 +1164,9 @@
         <v>30</v>
       </c>
       <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="G7" t="s">
@@ -1146,7 +1176,7 @@
         <v>53</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1158,7 +1188,9 @@
         <v>7</v>
       </c>
       <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="N8" s="2"/>
@@ -1171,7 +1203,9 @@
         <v>26</v>
       </c>
       <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="N9" s="3"/>
@@ -1184,14 +1218,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="C10" s="8">
+        <v>8</v>
+      </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
       <c r="G10" t="s">
         <v>42</v>
       </c>
       <c r="H10">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1202,15 +1238,19 @@
       <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="B11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="8">
+        <v>4</v>
+      </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="G11" t="s">
         <v>47</v>
       </c>
-      <c r="H11">
-        <v>36</v>
+      <c r="H11" t="s">
+        <v>79</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1222,14 +1262,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="8">
+        <v>4</v>
+      </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="G12" t="s">
         <v>51</v>
       </c>
       <c r="H12">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1241,14 +1283,16 @@
         <v>18</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="8">
+        <v>2</v>
+      </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="G13" t="s">
         <v>43</v>
       </c>
       <c r="H13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1260,7 +1304,9 @@
         <v>25</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="N14" s="3"/>
@@ -1273,7 +1319,9 @@
         <v>27</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="N15" s="2"/>
@@ -1286,7 +1334,9 @@
         <v>28</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="C16" s="8">
+        <v>2</v>
+      </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="N16" s="2"/>
@@ -1299,7 +1349,9 @@
         <v>29</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="C17" s="8">
+        <v>2</v>
+      </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="N17" s="2"/>
@@ -1312,7 +1364,9 @@
         <v>17</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="N18" s="2"/>
@@ -1325,7 +1379,9 @@
         <v>24</v>
       </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="C19" s="8">
+        <v>1</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="N19" s="1"/>
@@ -1338,7 +1394,9 @@
         <v>23</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="N20" s="2"/>
@@ -1354,7 +1412,7 @@
         <v>43</v>
       </c>
       <c r="C21" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -1368,7 +1426,9 @@
         <v>50</v>
       </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="C22" s="8">
+        <v>2</v>
+      </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="N22" s="2"/>
@@ -1381,7 +1441,9 @@
         <v>38</v>
       </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="N23" s="3"/>
@@ -1397,7 +1459,7 @@
         <v>43</v>
       </c>
       <c r="C24" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
@@ -1411,7 +1473,9 @@
         <v>11</v>
       </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="N25" s="1"/>
@@ -1424,7 +1488,9 @@
         <v>21</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="C26" s="8">
+        <v>3</v>
+      </c>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="N26" s="1"/>
@@ -1437,7 +1503,9 @@
         <v>74</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="C27" s="8">
+        <v>4</v>
+      </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="N27" s="1"/>
@@ -1450,7 +1518,9 @@
         <v>45</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="N28" s="3"/>
@@ -1463,7 +1533,9 @@
         <v>46</v>
       </c>
       <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="N29" s="1"/>
@@ -1478,7 +1550,9 @@
       <c r="B30" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="13"/>
+      <c r="C30" s="13">
+        <v>34</v>
+      </c>
       <c r="D30" s="13"/>
       <c r="E30" s="13"/>
       <c r="N30" s="3"/>
@@ -1508,7 +1582,9 @@
         <v>39</v>
       </c>
       <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+      <c r="C32" s="8">
+        <v>8</v>
+      </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="N32" s="3"/>
@@ -1521,7 +1597,9 @@
         <v>40</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="N33" s="1"/>
@@ -1570,8 +1648,8 @@
       <c r="B36" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="13">
-        <v>8</v>
+      <c r="C36" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="13"/>
@@ -1585,7 +1663,9 @@
         <v>49</v>
       </c>
       <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+      <c r="C37" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="N37" s="2"/>
@@ -1601,7 +1681,7 @@
         <v>69</v>
       </c>
       <c r="C38" s="13">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D38" s="13"/>
       <c r="E38" s="13"/>
@@ -1615,7 +1695,9 @@
         <v>64</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="C39" s="8">
+        <v>3</v>
+      </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="N39" s="2"/>
@@ -1628,7 +1710,9 @@
         <v>65</v>
       </c>
       <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
+      <c r="C40" s="8">
+        <v>3</v>
+      </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="N40" s="2"/>
@@ -1641,7 +1725,9 @@
         <v>67</v>
       </c>
       <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
+      <c r="C41" s="8">
+        <v>3</v>
+      </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="N41" s="1"/>
@@ -1654,7 +1740,9 @@
         <v>66</v>
       </c>
       <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
+      <c r="C42" s="8">
+        <v>3</v>
+      </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="N42" s="1"/>
@@ -1670,7 +1758,7 @@
         <v>47</v>
       </c>
       <c r="C43" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
@@ -1680,34 +1768,34 @@
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="8">
+      <c r="C44" s="13">
         <v>8</v>
       </c>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="8">
+      <c r="C45" s="13">
         <v>2</v>
       </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\foler\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71ADBF9-A241-431A-B281-3D175479358F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FAD7CB-C18D-4F71-8995-D5FD25571451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="81">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -542,7 +542,14 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>36(カードUI周りはベータ)</t>
+    <t>済</t>
+    <rPh sb="0" eb="1">
+      <t>スミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>１6(カードUI周りはベータ)</t>
     <rPh sb="8" eb="9">
       <t>マワ</t>
     </rPh>
@@ -1245,12 +1252,14 @@
         <v>4</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="E11" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="G11" t="s">
         <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1601,7 +1610,9 @@
         <v>2</v>
       </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="E33" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -1729,7 +1740,9 @@
         <v>3</v>
       </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
+      <c r="E41" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -1744,7 +1757,9 @@
         <v>3</v>
       </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
+      <c r="E42" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -1761,7 +1776,9 @@
         <v>4</v>
       </c>
       <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="E43" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -1778,7 +1795,9 @@
         <v>8</v>
       </c>
       <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="E44" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\foler\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FAD7CB-C18D-4F71-8995-D5FD25571451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3A2A76-AEDF-4152-A758-EF51542645F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="80">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -85,16 +85,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・攻撃と敵</t>
-    <rPh sb="1" eb="3">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・移動</t>
     <rPh sb="1" eb="3">
       <t>イドウ</t>
@@ -527,14 +517,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>なし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>26（一人当たり）</t>
     <rPh sb="3" eb="6">
       <t>ヒトリア</t>
@@ -542,16 +524,30 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>済</t>
-    <rPh sb="0" eb="1">
-      <t>スミ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>１6(カードUI周りはベータ)</t>
     <rPh sb="8" eb="9">
       <t>マワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4(麻生)</t>
+    <rPh sb="2" eb="4">
+      <t>アソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -681,7 +677,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -712,6 +708,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,33 +1084,33 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>35</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="E1" s="14"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
       </c>
       <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="8" t="s">
@@ -1116,10 +1118,11 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="8" t="s">
@@ -1130,36 +1133,37 @@
         <v>1</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="8" t="s">
-        <v>6</v>
-      </c>
+      <c r="A5" s="8"/>
       <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
-        <v>77</v>
-      </c>
+      <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="13">
         <v>11</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="D6" s="13">
+        <v>11</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
       <c r="G6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1168,22 +1172,23 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1192,14 +1197,15 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" s="8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1207,14 +1213,15 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1222,16 +1229,19 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8">
         <v>8</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="8">
+        <v>4</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
       <c r="G10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H10">
         <v>18</v>
@@ -1243,23 +1253,24 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="8">
         <v>4</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="D11" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
       <c r="G11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1268,16 +1279,17 @@
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8">
         <v>4</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15"/>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>16</v>
@@ -1289,16 +1301,17 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8">
         <v>2</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H13">
         <v>15</v>
@@ -1310,14 +1323,15 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8">
         <v>2</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1325,14 +1339,17 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
         <v>4</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
+      <c r="D15" s="8">
+        <v>4</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1340,14 +1357,15 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8">
         <v>2</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -1355,14 +1373,15 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8">
         <v>2</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -1370,14 +1389,17 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8">
         <v>1</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1385,14 +1407,17 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
         <v>1</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1400,14 +1425,17 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
         <v>1</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="D20" s="8">
+        <v>1</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -1415,16 +1443,19 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="13">
         <v>4</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="13">
+        <v>4</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1432,14 +1463,17 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8">
         <v>2</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="D22" s="8">
+        <v>2</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -1447,14 +1481,17 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
         <v>2</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="D23" s="8">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1465,13 +1502,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="13">
         <v>11</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="13">
+        <v>11</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1479,14 +1519,15 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -1494,14 +1535,17 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8">
         <v>3</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
+      <c r="D26" s="8">
+        <v>3</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -1509,14 +1553,17 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8">
         <v>4</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
+      <c r="D27" s="8">
+        <v>4</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -1524,14 +1571,17 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8">
         <v>2</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="D28" s="8">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1539,14 +1589,17 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8">
         <v>2</v>
       </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="D29" s="8">
+        <v>2</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -1554,16 +1607,19 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C30" s="13">
         <v>34</v>
       </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="D30" s="13">
+        <v>32</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="15"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -1571,16 +1627,19 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="8">
         <v>8</v>
       </c>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="D31" s="8">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -1588,14 +1647,17 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8">
         <v>8</v>
       </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="D32" s="8">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="15"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -1603,16 +1665,15 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="8">
-        <v>2</v>
+      <c r="C33" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="15"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -1620,16 +1681,19 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C34" s="8">
         <v>8</v>
       </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
+      <c r="D34" s="8">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="15"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -1637,16 +1701,19 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C35" s="8">
         <v>8</v>
       </c>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
+      <c r="D35" s="8">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="15"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -1654,16 +1721,17 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="15"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
@@ -1671,14 +1739,15 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -1686,16 +1755,19 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C38" s="13">
         <v>12</v>
       </c>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="D38" s="13">
+        <v>6</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -1703,14 +1775,17 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8">
         <v>3</v>
       </c>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
+      <c r="D39" s="8">
+        <v>3</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -1718,14 +1793,17 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8">
         <v>3</v>
       </c>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
+      <c r="D40" s="8">
+        <v>3</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -1733,16 +1811,15 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" s="8"/>
-      <c r="C41" s="8">
-        <v>3</v>
+      <c r="C41" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="15"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -1750,16 +1827,15 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="8"/>
-      <c r="C42" s="8">
-        <v>3</v>
+      <c r="C42" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="8" t="s">
-        <v>79</v>
-      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="15"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -1767,18 +1843,17 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" s="13">
-        <v>4</v>
+        <v>46</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="D43" s="13"/>
-      <c r="E43" s="13" t="s">
-        <v>79</v>
-      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="15"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -1786,18 +1861,17 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" s="13">
-        <v>8</v>
+        <v>46</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="D44" s="13"/>
-      <c r="E44" s="13" t="s">
-        <v>79</v>
-      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="15"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -1808,13 +1882,16 @@
         <v>3</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="13">
         <v>2</v>
       </c>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="D45" s="13">
+        <v>2</v>
+      </c>
+      <c r="E45" s="14"/>
+      <c r="F45" s="15"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -1825,13 +1902,16 @@
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="15"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
     </row>
     <row r="47" spans="1:17">
+      <c r="E47" s="14"/>
+      <c r="F47" s="15"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -1841,6 +1921,8 @@
       <c r="A48" t="s">
         <v>2</v>
       </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -1848,8 +1930,10 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" t="s">
-        <v>12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
@@ -1857,7 +1941,7 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -1866,7 +1950,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -1875,7 +1959,7 @@
     </row>
     <row r="52" spans="1:17">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -1884,7 +1968,7 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -1999,19 +2083,19 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>34</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:10">
@@ -2035,10 +2119,10 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -2048,13 +2132,13 @@
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -2078,7 +2162,7 @@
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I9">
         <v>21</v>
@@ -2091,7 +2175,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="H10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10">
         <v>23</v>
@@ -2104,7 +2188,7 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I11">
         <v>32</v>
@@ -2117,7 +2201,7 @@
       <c r="E12" s="8"/>
       <c r="F12" s="8"/>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -2525,30 +2609,30 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>55</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>56</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>57</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>58</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>59</v>
-      </c>
-      <c r="H2" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -2570,7 +2654,7 @@
       <c r="H4" s="9"/>
       <c r="J4" s="6"/>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2602,7 +2686,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="9">
         <v>31</v>
@@ -2654,7 +2738,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\foler\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F3A2A76-AEDF-4152-A758-EF51542645F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8552FE4-D60F-4C9B-83AB-774A32509A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -520,13 +520,6 @@
     <t>26（一人当たり）</t>
     <rPh sb="3" eb="6">
       <t>ヒトリア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>１6(カードUI周りはベータ)</t>
-    <rPh sb="8" eb="9">
-      <t>マワ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -677,7 +670,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -710,10 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1093,10 +1083,9 @@
         <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E1" s="14"/>
-      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="13" t="s">
@@ -1110,7 +1099,6 @@
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="14"/>
-      <c r="F2" s="15"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="8" t="s">
@@ -1118,11 +1106,10 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="8" t="s">
@@ -1134,7 +1121,6 @@
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="14"/>
-      <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="8"/>
@@ -1142,7 +1128,6 @@
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="13" t="s">
@@ -1158,7 +1143,6 @@
         <v>11</v>
       </c>
       <c r="E6" s="14"/>
-      <c r="F6" s="15"/>
       <c r="G6" t="s">
         <v>31</v>
       </c>
@@ -1176,11 +1160,10 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="15"/>
       <c r="G7" t="s">
         <v>32</v>
       </c>
@@ -1201,11 +1184,10 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="15"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1217,11 +1199,10 @@
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="15"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1239,7 +1220,6 @@
         <v>4</v>
       </c>
       <c r="E10" s="14"/>
-      <c r="F10" s="15"/>
       <c r="G10" t="s">
         <v>41</v>
       </c>
@@ -1262,15 +1242,14 @@
         <v>4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" s="14"/>
-      <c r="F11" s="15"/>
       <c r="G11" t="s">
         <v>46</v>
       </c>
-      <c r="H11" t="s">
-        <v>76</v>
+      <c r="H11">
+        <v>16</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1287,7 +1266,6 @@
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
       <c r="G12" t="s">
         <v>50</v>
       </c>
@@ -1309,7 +1287,6 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="14"/>
-      <c r="F13" s="15"/>
       <c r="G13" t="s">
         <v>42</v>
       </c>
@@ -1331,7 +1308,6 @@
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="14"/>
-      <c r="F14" s="15"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1349,7 +1325,6 @@
         <v>4</v>
       </c>
       <c r="E15" s="14"/>
-      <c r="F15" s="15"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1365,7 +1340,6 @@
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -1381,7 +1355,6 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="14"/>
-      <c r="F17" s="15"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -1399,7 +1372,6 @@
         <v>1</v>
       </c>
       <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1417,7 +1389,6 @@
         <v>1</v>
       </c>
       <c r="E19" s="14"/>
-      <c r="F19" s="15"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1435,7 +1406,6 @@
         <v>1</v>
       </c>
       <c r="E20" s="14"/>
-      <c r="F20" s="15"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -1455,7 +1425,6 @@
         <v>4</v>
       </c>
       <c r="E21" s="14"/>
-      <c r="F21" s="15"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1473,7 +1442,6 @@
         <v>2</v>
       </c>
       <c r="E22" s="14"/>
-      <c r="F22" s="15"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -1491,7 +1459,6 @@
         <v>2</v>
       </c>
       <c r="E23" s="14"/>
-      <c r="F23" s="15"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1511,7 +1478,6 @@
         <v>11</v>
       </c>
       <c r="E24" s="14"/>
-      <c r="F24" s="15"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1523,11 +1489,10 @@
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="14"/>
-      <c r="F25" s="15"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -1545,7 +1510,6 @@
         <v>3</v>
       </c>
       <c r="E26" s="14"/>
-      <c r="F26" s="15"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -1563,7 +1527,6 @@
         <v>4</v>
       </c>
       <c r="E27" s="14"/>
-      <c r="F27" s="15"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -1581,7 +1544,6 @@
         <v>2</v>
       </c>
       <c r="E28" s="14"/>
-      <c r="F28" s="15"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1599,7 +1561,6 @@
         <v>2</v>
       </c>
       <c r="E29" s="14"/>
-      <c r="F29" s="15"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -1619,7 +1580,6 @@
         <v>32</v>
       </c>
       <c r="E30" s="14"/>
-      <c r="F30" s="15"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -1639,7 +1599,6 @@
         <v>8</v>
       </c>
       <c r="E31" s="14"/>
-      <c r="F31" s="15"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -1657,7 +1616,6 @@
         <v>8</v>
       </c>
       <c r="E32" s="14"/>
-      <c r="F32" s="15"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -1669,11 +1627,10 @@
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="14"/>
-      <c r="F33" s="15"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -1693,7 +1650,6 @@
         <v>8</v>
       </c>
       <c r="E34" s="14"/>
-      <c r="F34" s="15"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -1713,7 +1669,6 @@
         <v>8</v>
       </c>
       <c r="E35" s="14"/>
-      <c r="F35" s="15"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -1727,11 +1682,10 @@
         <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
-      <c r="F36" s="15"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
@@ -1743,11 +1697,10 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="14"/>
-      <c r="F37" s="15"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -1767,7 +1720,6 @@
         <v>6</v>
       </c>
       <c r="E38" s="14"/>
-      <c r="F38" s="15"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -1785,7 +1737,6 @@
         <v>3</v>
       </c>
       <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -1803,7 +1754,6 @@
         <v>3</v>
       </c>
       <c r="E40" s="14"/>
-      <c r="F40" s="15"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -1815,11 +1765,10 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="14"/>
-      <c r="F41" s="15"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -1831,11 +1780,10 @@
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="14"/>
-      <c r="F42" s="15"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -1849,11 +1797,10 @@
         <v>46</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="14"/>
-      <c r="F43" s="15"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -1867,11 +1814,10 @@
         <v>46</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="14"/>
-      <c r="F44" s="15"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -1891,7 +1837,6 @@
         <v>2</v>
       </c>
       <c r="E45" s="14"/>
-      <c r="F45" s="15"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -1903,7 +1848,6 @@
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
       <c r="E46" s="14"/>
-      <c r="F46" s="15"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
@@ -1911,7 +1855,6 @@
     </row>
     <row r="47" spans="1:17">
       <c r="E47" s="14"/>
-      <c r="F47" s="15"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -1921,8 +1864,6 @@
       <c r="A48" t="s">
         <v>2</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -1932,8 +1873,6 @@
       <c r="A49" t="s">
         <v>11</v>
       </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\foler\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8552FE4-D60F-4C9B-83AB-774A32509A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5CD874-852D-4759-8F81-EEA6752458EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="79">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1643,12 +1643,10 @@
       <c r="B34" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="8">
-        <v>8</v>
-      </c>
-      <c r="D34" s="8">
-        <v>8</v>
-      </c>
+      <c r="C34" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D34" s="8"/>
       <c r="E34" s="14"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5CD874-852D-4759-8F81-EEA6752458EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D15BA8-E0C2-4485-90F9-134EE447EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -531,17 +531,18 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>4(麻生)</t>
-    <rPh sb="2" eb="4">
-      <t>アソウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>残コスト</t>
     <rPh sb="0" eb="1">
       <t>ノコ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -703,7 +704,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1083,7 +1084,7 @@
         <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E1" s="14"/>
     </row>
@@ -1116,8 +1117,8 @@
         <v>5</v>
       </c>
       <c r="B4" s="8"/>
-      <c r="C4" s="8">
-        <v>1</v>
+      <c r="C4" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="14"/>
@@ -1140,7 +1141,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="13">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E6" s="14"/>
       <c r="G6" t="s">
@@ -1216,15 +1217,15 @@
       <c r="C10" s="8">
         <v>8</v>
       </c>
-      <c r="D10" s="8">
-        <v>4</v>
+      <c r="D10" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E10" s="14"/>
       <c r="G10" t="s">
         <v>41</v>
       </c>
       <c r="H10">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1238,18 +1239,18 @@
       <c r="B11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="8">
-        <v>4</v>
+      <c r="C11" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" s="14"/>
       <c r="G11" t="s">
         <v>46</v>
       </c>
       <c r="H11">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -1261,8 +1262,8 @@
         <v>9</v>
       </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="8">
-        <v>4</v>
+      <c r="C12" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="14"/>
@@ -1270,7 +1271,7 @@
         <v>50</v>
       </c>
       <c r="H12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -1282,8 +1283,8 @@
         <v>17</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="8">
-        <v>2</v>
+      <c r="C13" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="14"/>
@@ -1291,7 +1292,7 @@
         <v>42</v>
       </c>
       <c r="H13">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -1303,8 +1304,8 @@
         <v>24</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="8">
-        <v>2</v>
+      <c r="C14" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D14" s="8"/>
       <c r="E14" s="14"/>
@@ -1321,8 +1322,8 @@
       <c r="C15" s="8">
         <v>4</v>
       </c>
-      <c r="D15" s="8">
-        <v>4</v>
+      <c r="D15" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E15" s="14"/>
       <c r="N15" s="2"/>
@@ -1335,8 +1336,8 @@
         <v>27</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="8">
-        <v>2</v>
+      <c r="C16" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="14"/>
@@ -1350,8 +1351,8 @@
         <v>28</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="8">
-        <v>2</v>
+      <c r="C17" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="14"/>
@@ -1365,11 +1366,11 @@
         <v>16</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
+      <c r="C18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E18" s="14"/>
       <c r="N18" s="2"/>
@@ -1382,11 +1383,11 @@
         <v>23</v>
       </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>1</v>
+      <c r="C19" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E19" s="14"/>
       <c r="N19" s="1"/>
@@ -1475,7 +1476,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="13">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E24" s="14"/>
       <c r="N24" s="1"/>
@@ -1503,11 +1504,11 @@
         <v>20</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="8">
-        <v>3</v>
-      </c>
-      <c r="D26" s="8">
-        <v>3</v>
+      <c r="C26" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E26" s="14"/>
       <c r="N26" s="1"/>
@@ -1520,11 +1521,11 @@
         <v>73</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="8">
-        <v>4</v>
-      </c>
-      <c r="D27" s="8">
-        <v>4</v>
+      <c r="C27" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E27" s="14"/>
       <c r="N27" s="1"/>
@@ -1537,11 +1538,11 @@
         <v>44</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="8">
-        <v>2</v>
-      </c>
-      <c r="D28" s="8">
-        <v>2</v>
+      <c r="C28" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="E28" s="14"/>
       <c r="N28" s="3"/>
@@ -1577,7 +1578,7 @@
         <v>34</v>
       </c>
       <c r="D30" s="13">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E30" s="14"/>
       <c r="N30" s="3"/>
@@ -1592,11 +1593,11 @@
       <c r="B31" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="8">
-        <v>8</v>
-      </c>
-      <c r="D31" s="8">
-        <v>8</v>
+      <c r="C31" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E31" s="14"/>
       <c r="N31" s="3"/>
@@ -1609,11 +1610,11 @@
         <v>38</v>
       </c>
       <c r="B32" s="8"/>
-      <c r="C32" s="8">
-        <v>8</v>
-      </c>
-      <c r="D32" s="8">
-        <v>8</v>
+      <c r="C32" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E32" s="14"/>
       <c r="N32" s="3"/>
@@ -1660,12 +1661,10 @@
       <c r="B35" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="8">
-        <v>8</v>
-      </c>
-      <c r="D35" s="8">
-        <v>8</v>
-      </c>
+      <c r="C35" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D35" s="8"/>
       <c r="E35" s="14"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D15BA8-E0C2-4485-90F9-134EE447EA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A78D011-3E12-476A-BEC4-B4A246C160EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="80">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -671,7 +671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,9 +702,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1086,7 +1083,6 @@
       <c r="D1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="13" t="s">
@@ -1099,7 +1095,6 @@
         <v>1</v>
       </c>
       <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="8" t="s">
@@ -1110,7 +1105,6 @@
         <v>76</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="8" t="s">
@@ -1121,14 +1115,12 @@
         <v>76</v>
       </c>
       <c r="D4" s="8"/>
-      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="13" t="s">
@@ -1143,7 +1135,6 @@
       <c r="D6" s="13">
         <v>1</v>
       </c>
-      <c r="E6" s="14"/>
       <c r="G6" t="s">
         <v>31</v>
       </c>
@@ -1164,7 +1155,6 @@
         <v>76</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="14"/>
       <c r="G7" t="s">
         <v>32</v>
       </c>
@@ -1188,7 +1178,6 @@
         <v>76</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="14"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1203,7 +1192,6 @@
         <v>76</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="14"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1220,7 +1208,6 @@
       <c r="D10" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="14"/>
       <c r="G10" t="s">
         <v>41</v>
       </c>
@@ -1245,7 +1232,6 @@
       <c r="D11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="14"/>
       <c r="G11" t="s">
         <v>46</v>
       </c>
@@ -1266,7 +1252,6 @@
         <v>76</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="14"/>
       <c r="G12" t="s">
         <v>50</v>
       </c>
@@ -1287,7 +1272,6 @@
         <v>76</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="14"/>
       <c r="G13" t="s">
         <v>42</v>
       </c>
@@ -1308,7 +1292,6 @@
         <v>76</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="14"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1325,7 +1308,6 @@
       <c r="D15" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="14"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1340,7 +1322,6 @@
         <v>76</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="14"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -1355,7 +1336,6 @@
         <v>76</v>
       </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -1372,7 +1352,6 @@
       <c r="D18" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="14"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1389,7 +1368,6 @@
       <c r="D19" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="14"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
@@ -1406,7 +1384,6 @@
       <c r="D20" s="8">
         <v>1</v>
       </c>
-      <c r="E20" s="14"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -1425,7 +1402,6 @@
       <c r="D21" s="13">
         <v>4</v>
       </c>
-      <c r="E21" s="14"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1442,7 +1418,6 @@
       <c r="D22" s="8">
         <v>2</v>
       </c>
-      <c r="E22" s="14"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -1459,7 +1434,6 @@
       <c r="D23" s="8">
         <v>2</v>
       </c>
-      <c r="E23" s="14"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
@@ -1478,7 +1452,6 @@
       <c r="D24" s="13">
         <v>2</v>
       </c>
-      <c r="E24" s="14"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
@@ -1493,7 +1466,6 @@
         <v>76</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="14"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
@@ -1510,7 +1482,6 @@
       <c r="D26" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="14"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -1527,7 +1498,6 @@
       <c r="D27" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="14"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
@@ -1544,7 +1514,6 @@
       <c r="D28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E28" s="14"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
@@ -1561,7 +1530,6 @@
       <c r="D29" s="8">
         <v>2</v>
       </c>
-      <c r="E29" s="14"/>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
@@ -1580,7 +1548,6 @@
       <c r="D30" s="13">
         <v>0</v>
       </c>
-      <c r="E30" s="14"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -1599,7 +1566,6 @@
       <c r="D31" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="14"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
@@ -1616,7 +1582,6 @@
       <c r="D32" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E32" s="14"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
@@ -1631,7 +1596,6 @@
         <v>76</v>
       </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="14"/>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -1648,7 +1612,6 @@
         <v>76</v>
       </c>
       <c r="D34" s="8"/>
-      <c r="E34" s="14"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -1665,7 +1628,6 @@
         <v>76</v>
       </c>
       <c r="D35" s="8"/>
-      <c r="E35" s="14"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" s="2"/>
@@ -1682,7 +1644,6 @@
         <v>76</v>
       </c>
       <c r="D36" s="13"/>
-      <c r="E36" s="14"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
@@ -1697,7 +1658,6 @@
         <v>76</v>
       </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="14"/>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -1713,10 +1673,7 @@
       <c r="C38" s="13">
         <v>12</v>
       </c>
-      <c r="D38" s="13">
-        <v>6</v>
-      </c>
-      <c r="E38" s="14"/>
+      <c r="D38" s="13"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
@@ -1727,13 +1684,10 @@
         <v>63</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="8">
-        <v>3</v>
-      </c>
-      <c r="D39" s="8">
-        <v>3</v>
-      </c>
-      <c r="E39" s="14"/>
+      <c r="C39" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="8"/>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" s="2"/>
@@ -1744,13 +1698,10 @@
         <v>64</v>
       </c>
       <c r="B40" s="8"/>
-      <c r="C40" s="8">
-        <v>3</v>
-      </c>
-      <c r="D40" s="8">
-        <v>3</v>
-      </c>
-      <c r="E40" s="14"/>
+      <c r="C40" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D40" s="8"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" s="2"/>
@@ -1765,7 +1716,6 @@
         <v>76</v>
       </c>
       <c r="D41" s="8"/>
-      <c r="E41" s="14"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -1780,7 +1730,6 @@
         <v>76</v>
       </c>
       <c r="D42" s="8"/>
-      <c r="E42" s="14"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -1797,7 +1746,6 @@
         <v>76</v>
       </c>
       <c r="D43" s="13"/>
-      <c r="E43" s="14"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -1814,7 +1762,6 @@
         <v>76</v>
       </c>
       <c r="D44" s="13"/>
-      <c r="E44" s="14"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
@@ -1827,13 +1774,10 @@
       <c r="B45" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="13">
-        <v>2</v>
-      </c>
-      <c r="D45" s="13">
-        <v>2</v>
-      </c>
-      <c r="E45" s="14"/>
+      <c r="C45" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="13"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
@@ -1844,14 +1788,12 @@
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
-      <c r="E46" s="14"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="1"/>
     </row>
     <row r="47" spans="1:17">
-      <c r="E47" s="14"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -2100,9 +2042,6 @@
       <c r="H9" t="s">
         <v>41</v>
       </c>
-      <c r="I9">
-        <v>21</v>
-      </c>
     </row>
     <row r="10" spans="2:10">
       <c r="B10" s="13"/>
@@ -2113,9 +2052,6 @@
       <c r="H10" t="s">
         <v>46</v>
       </c>
-      <c r="I10">
-        <v>23</v>
-      </c>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="8"/>
@@ -2126,9 +2062,6 @@
       <c r="H11" t="s">
         <v>50</v>
       </c>
-      <c r="I11">
-        <v>32</v>
-      </c>
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="8"/>
@@ -2138,9 +2071,6 @@
       <c r="F12" s="8"/>
       <c r="H12" t="s">
         <v>42</v>
-      </c>
-      <c r="I12">
-        <v>9</v>
       </c>
     </row>
     <row r="13" spans="2:10">

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A78D011-3E12-476A-BEC4-B4A246C160EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E55EDAF-CFEB-48AA-892B-B0B248A522F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -495,13 +493,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>34（一人当たり）</t>
-    <rPh sb="3" eb="6">
-      <t>ヒトリア</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アルファ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -543,6 +534,308 @@
   </si>
   <si>
     <t>　　</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→スタートボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・スタート画面</t>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ゲーム終了</t>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームオーバー画面</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→スタートに戻る</t>
+    <rPh sb="6" eb="7">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ゲームクリア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームシステム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→第一ステージ</t>
+    <rPh sb="1" eb="3">
+      <t>ダイイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→→ザコフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→→ストアフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→→ボスフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→第二ステージ</t>
+    <rPh sb="1" eb="2">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ニ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→第三ステージ</t>
+    <rPh sb="1" eb="2">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>サン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→所持カード保存</t>
+    <rPh sb="1" eb="3">
+      <t>ショジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→デッキ編集</t>
+    <rPh sb="4" eb="6">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→デッキカード保存</t>
+    <rPh sb="7" eb="9">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→選択カードのハイライト</t>
+    <rPh sb="1" eb="3">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→合成のガイド</t>
+    <rPh sb="1" eb="3">
+      <t>ゴウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→使用時演出</t>
+    <rPh sb="1" eb="4">
+      <t>シヨウジ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ストア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→カーソルの切り替え</t>
+    <rPh sb="6" eb="7">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード関連</t>
+    <rPh sb="3" eb="5">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→パック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵関連</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遠ザコ敵</t>
+    <rPh sb="0" eb="1">
+      <t>オン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>近ザコ敵のスクリプト使う</t>
+    <rPh sb="0" eb="1">
+      <t>コン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス敵１</t>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→移動</t>
+    <rPh sb="1" eb="3">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→攻撃1</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→攻撃2</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→攻撃3</t>
+    <rPh sb="1" eb="3">
+      <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス敵２</t>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボス敵３</t>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→HP、死亡</t>
+    <rPh sb="4" eb="6">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ダメージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー関連</t>
+    <rPh sb="5" eb="7">
+      <t>カンレン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡演出</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージ演出</t>
+    <rPh sb="4" eb="6">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>操作説明</t>
+    <rPh sb="0" eb="4">
+      <t>ソウサセツメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>58（一人当たり）</t>
+    <rPh sb="3" eb="6">
+      <t>ヒトリア</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -580,7 +873,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +934,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -671,7 +976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -702,6 +1007,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1081,7 +1395,7 @@
         <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -1102,7 +1416,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="8"/>
     </row>
@@ -1112,7 +1426,7 @@
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="8"/>
     </row>
@@ -1152,7 +1466,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8"/>
       <c r="G7" t="s">
@@ -1162,7 +1476,7 @@
         <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1175,7 +1489,7 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="8"/>
       <c r="N8" s="2"/>
@@ -1189,7 +1503,7 @@
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8"/>
       <c r="N9" s="3"/>
@@ -1206,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s">
         <v>41</v>
@@ -1227,10 +1541,10 @@
         <v>46</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
         <v>46</v>
@@ -1249,7 +1563,7 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" s="8"/>
       <c r="G12" t="s">
@@ -1269,7 +1583,7 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" s="8"/>
       <c r="G13" t="s">
@@ -1289,7 +1603,7 @@
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" s="8"/>
       <c r="N14" s="3"/>
@@ -1306,7 +1620,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -1319,7 +1633,7 @@
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="8"/>
       <c r="N16" s="2"/>
@@ -1333,7 +1647,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="8"/>
       <c r="N17" s="2"/>
@@ -1347,10 +1661,10 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1363,10 +1677,10 @@
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1463,7 +1777,7 @@
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D25" s="8"/>
       <c r="N25" s="1"/>
@@ -1477,10 +1791,10 @@
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1489,14 +1803,14 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1509,10 +1823,10 @@
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1561,10 +1875,10 @@
         <v>46</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1577,10 +1891,10 @@
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1593,7 +1907,7 @@
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D33" s="8"/>
       <c r="N33" s="1"/>
@@ -1609,7 +1923,7 @@
         <v>50</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D34" s="8"/>
       <c r="N34" s="1"/>
@@ -1625,7 +1939,7 @@
         <v>50</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D35" s="8"/>
       <c r="N35" s="2"/>
@@ -1641,7 +1955,7 @@
         <v>50</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D36" s="13"/>
       <c r="N36" s="4"/>
@@ -1655,7 +1969,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D37" s="8"/>
       <c r="N37" s="2"/>
@@ -1665,7 +1979,7 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>68</v>
@@ -1685,7 +1999,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D39" s="8"/>
       <c r="N39" s="2"/>
@@ -1699,7 +2013,7 @@
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D40" s="8"/>
       <c r="N40" s="2"/>
@@ -1713,7 +2027,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D41" s="8"/>
       <c r="N41" s="1"/>
@@ -1727,7 +2041,7 @@
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D42" s="8"/>
       <c r="N42" s="1"/>
@@ -1743,7 +2057,7 @@
         <v>46</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D43" s="13"/>
       <c r="N43" s="1"/>
@@ -1759,7 +2073,7 @@
         <v>46</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D44" s="13"/>
       <c r="N44" s="1"/>
@@ -1775,7 +2089,7 @@
         <v>46</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D45" s="13"/>
       <c r="N45" s="1"/>
@@ -1945,14 +2259,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E21B2F-17A7-4263-AC36-EBB7CC62FACB}">
-  <dimension ref="B2:J67"/>
+  <dimension ref="B2:J76"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="17.75" customWidth="1"/>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="3" max="3" width="14.375" customWidth="1"/>
     <col min="4" max="4" width="12.375" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="11.75" customWidth="1"/>
+    <col min="7" max="7" width="23.375" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
     <col min="9" max="9" width="11.625" customWidth="1"/>
     <col min="10" max="10" width="14.375" customWidth="1"/>
@@ -1961,7 +2276,7 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>40</v>
@@ -1977,38 +2292,46 @@
       </c>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="13"/>
+      <c r="B3" s="13" t="s">
+        <v>79</v>
+      </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="B4" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="B5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
       <c r="H5" t="s">
         <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="2:10">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="B6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
       <c r="H6" t="s">
         <v>32</v>
       </c>
@@ -2016,447 +2339,629 @@
         <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="B7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="B8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="2:10">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="B9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
       <c r="H9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="B10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
       <c r="H10" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="B11" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
       <c r="H11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="B12" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="H12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="B13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
     </row>
     <row r="14" spans="2:10">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="2:10">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="B15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="B16" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+      <c r="B17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="2"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
+      <c r="B18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="B19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="B20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
+      <c r="B21" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="B22" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
+      <c r="B24" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
+      <c r="B25" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="B26" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
+      <c r="B27" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
+      <c r="B28" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
+      <c r="B29" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="B30" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
+      <c r="B31" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="2:6">
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-    </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
+      <c r="B32" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
     </row>
     <row r="49" spans="2:6">
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
+      <c r="B49" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="9"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="B50" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
+      <c r="B51" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
+      <c r="B52" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
     </row>
     <row r="53" spans="2:6">
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
+      <c r="B53" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="9"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="B54" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
+      <c r="B55" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
     </row>
     <row r="56" spans="2:6">
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
+      <c r="B56" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="9"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
+      <c r="B57" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
+      <c r="B58" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
     </row>
     <row r="59" spans="2:6">
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B59" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
+      <c r="B60" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
+      <c r="B61" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
+      <c r="B62" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
+      <c r="B63" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
+      <c r="B64" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
     </row>
     <row r="65" spans="2:6">
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
     </row>
     <row r="66" spans="2:6">
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" spans="2:6">
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="14"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="14"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="14"/>
+      <c r="C72" s="14"/>
+      <c r="D72" s="14"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+    </row>
+    <row r="73" spans="2:6">
+      <c r="B73" s="14"/>
+      <c r="C73" s="14"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+    </row>
+    <row r="74" spans="2:6">
+      <c r="B74" s="14"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+    </row>
+    <row r="75" spans="2:6">
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+    </row>
+    <row r="76" spans="2:6">
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -2515,49 +3020,49 @@
       <c r="E4" s="8">
         <v>6</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
       <c r="J4" s="6"/>
       <c r="K4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="15">
         <v>31</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="16">
         <v>1</v>
       </c>
       <c r="D8" s="10"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumu0\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E55EDAF-CFEB-48AA-892B-B0B248A522F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4A8266-A835-456D-91AF-21BA11409AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="141">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -588,17 +588,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>→第一ステージ</t>
-    <rPh sb="1" eb="3">
-      <t>ダイイチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>→→ザコフェーズ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>→→ストアフェーズ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -836,6 +825,161 @@
     <rPh sb="3" eb="6">
       <t>ヒトリア</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージのフェーズ進行</t>
+    <rPh sb="9" eb="11">
+      <t>シンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. ストアフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2. 雑魚敵フェーズ</t>
+    <rPh sb="3" eb="5">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. 雑魚敵フェーズ</t>
+    <rPh sb="3" eb="5">
+      <t>ザコ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4. ボスフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - パックの購入とデッキの編集</t>
+    <rPh sb="7" eb="9">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 時間内に敵を倒しまくる</t>
+    <rPh sb="3" eb="5">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - ボスを倒したらクリア</t>
+    <rPh sb="6" eb="7">
+      <t>タオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボスフェーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間制限を設ける？</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間経過とともにボスを強化</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケイカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>キョウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ラスボスは麻生？</t>
+    <rPh sb="5" eb="7">
+      <t>アソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寺尾</t>
+    <rPh sb="0" eb="2">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→行動</t>
+    <rPh sb="1" eb="3">
+      <t>コウドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→フェーズ処理</t>
+    <rPh sb="5" eb="7">
+      <t>ショリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→→ザコフェーズ1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→→ザコフェーズ2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→第一ステージ</t>
+    <rPh sb="1" eb="2">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>26, 36</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -873,7 +1017,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -946,8 +1090,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -970,13 +1120,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1016,6 +1177,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2259,7 +2426,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E21B2F-17A7-4263-AC36-EBB7CC62FACB}">
-  <dimension ref="B2:J76"/>
+  <dimension ref="B2:N73"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -2274,7 +2441,7 @@
     <col min="11" max="11" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:14">
       <c r="B2" s="8" t="s">
         <v>71</v>
       </c>
@@ -2290,17 +2457,28 @@
       <c r="F2" s="8" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="2:10">
+      <c r="G2" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="N2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
-    </row>
-    <row r="4" spans="2:10">
+      <c r="N3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4" s="7" t="s">
         <v>81</v>
       </c>
@@ -2308,8 +2486,11 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-    </row>
-    <row r="5" spans="2:10">
+      <c r="N4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5" s="7" t="s">
         <v>80</v>
       </c>
@@ -2317,14 +2498,17 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="2:10">
+      <c r="N5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6" s="7" t="s">
         <v>82</v>
       </c>
@@ -2332,17 +2516,20 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>32</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>52</v>
       </c>
-      <c r="J6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10">
+      <c r="K6" t="s">
+        <v>120</v>
+      </c>
+      <c r="N6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7" s="7" t="s">
         <v>83</v>
       </c>
@@ -2350,8 +2537,11 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="2:10">
+      <c r="N7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8" s="7" t="s">
         <v>84</v>
       </c>
@@ -2359,8 +2549,11 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="2:10">
+      <c r="N8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9" s="7" t="s">
         <v>85</v>
       </c>
@@ -2368,11 +2561,17 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="2:10">
+      <c r="J9">
+        <v>40</v>
+      </c>
+      <c r="N9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10" s="7" t="s">
         <v>84</v>
       </c>
@@ -2380,11 +2579,14 @@
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="11" spans="2:10">
+      <c r="J10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11" s="13" t="s">
         <v>86</v>
       </c>
@@ -2392,460 +2594,581 @@
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:14">
       <c r="B12" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="H12" t="s">
+      <c r="C12" s="9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="7" t="s">
+      <c r="D12" s="9">
+        <v>18</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
+      <c r="B13" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18">
+        <v>12</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+    </row>
+    <row r="14" spans="2:14">
+      <c r="B14" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="7" t="s">
-        <v>89</v>
-      </c>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
+      <c r="D14" s="7">
+        <v>2</v>
+      </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:14">
       <c r="B15" s="7" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
+      <c r="D15" s="7">
+        <v>4</v>
+      </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:14">
       <c r="B16" s="7" t="s">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+      <c r="D16" s="7">
+        <v>4</v>
+      </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="N16" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7">
+        <v>6</v>
+      </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="7" t="s">
-        <v>89</v>
+      <c r="N17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="18" t="s">
+        <v>139</v>
       </c>
       <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
+      <c r="D18" s="7">
+        <v>2</v>
+      </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="7" t="s">
+      <c r="N18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19" s="18" t="s">
         <v>90</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
+      <c r="D19" s="7">
+        <v>2</v>
+      </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="7" t="s">
+    <row r="20" spans="2:14">
+      <c r="B20" s="18" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
+      <c r="D20" s="7">
+        <v>2</v>
+      </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="2:6">
+    <row r="21" spans="2:14">
+      <c r="B21" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="9">
+        <v>51</v>
+      </c>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22" s="7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
+      <c r="D22" s="7">
+        <v>10</v>
+      </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:14">
       <c r="B23" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
+      <c r="D23" s="7">
+        <v>10</v>
+      </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:14">
       <c r="B24" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
+      <c r="D24" s="7">
+        <v>20</v>
+      </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:6">
-      <c r="B25" s="9" t="s">
-        <v>102</v>
+    <row r="25" spans="2:14">
+      <c r="B25" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="7">
+        <v>2</v>
+      </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:14">
       <c r="B26" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
+      <c r="D26" s="7">
+        <v>5</v>
+      </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:14">
       <c r="B27" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
+      <c r="D27" s="7">
+        <v>2</v>
+      </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:14">
       <c r="B28" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:6">
-      <c r="B29" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="2:6">
+    <row r="29" spans="2:14">
+      <c r="B29" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:14">
       <c r="B31" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
+    <row r="32" spans="2:14">
+      <c r="B32" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
+      <c r="B33" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="18">
+        <v>6</v>
+      </c>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="7" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
+      <c r="D34" s="7">
+        <v>4</v>
+      </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
+      <c r="G34" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="7" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
+      <c r="D35" s="7">
+        <v>2</v>
+      </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
+      <c r="B36" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18">
+        <v>20</v>
+      </c>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" spans="2:7">
       <c r="B37" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
+      <c r="D37" s="7">
+        <v>2</v>
+      </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
     <row r="38" spans="2:7">
       <c r="B38" s="7" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
+      <c r="D38" s="7">
+        <v>5</v>
+      </c>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-      <c r="G38" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="39" spans="2:7">
       <c r="B39" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
+      <c r="D39" s="7">
+        <v>5</v>
+      </c>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="D40" s="7">
+        <v>5</v>
+      </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
     <row r="42" spans="2:7">
       <c r="B42" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
+      <c r="D42" s="7">
+        <v>2</v>
+      </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
+      <c r="B43" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="18">
+        <v>18</v>
+      </c>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="2:7">
       <c r="B44" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="D44" s="7">
+        <v>4</v>
+      </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
+      <c r="D45" s="7">
+        <v>4</v>
+      </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
+      <c r="D46" s="7">
+        <v>4</v>
+      </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
+      <c r="D47" s="7">
+        <v>4</v>
+      </c>
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
     </row>
     <row r="48" spans="2:7">
       <c r="B48" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="D48" s="7">
+        <v>1</v>
+      </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="D49" s="7">
+        <v>1</v>
+      </c>
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
+      <c r="C50" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" s="18">
+        <v>18</v>
+      </c>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="7" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+      <c r="D51" s="7">
+        <v>4</v>
+      </c>
       <c r="E51" s="7"/>
       <c r="F51" s="7"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="7" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
+      <c r="D52" s="7">
+        <v>4</v>
+      </c>
       <c r="E52" s="7"/>
       <c r="F52" s="7"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="7" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
+      <c r="D53" s="7">
+        <v>4</v>
+      </c>
       <c r="E53" s="7"/>
       <c r="F53" s="7"/>
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
+      <c r="D54" s="7">
+        <v>4</v>
+      </c>
       <c r="E54" s="7"/>
       <c r="F54" s="7"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
+      <c r="D55" s="7">
+        <v>1</v>
+      </c>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
+      <c r="D56" s="7">
+        <v>1</v>
+      </c>
       <c r="E56" s="7"/>
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
+      <c r="B57" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D57" s="9">
+        <v>5</v>
+      </c>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
+      <c r="D58" s="7">
+        <v>2</v>
+      </c>
       <c r="E58" s="7"/>
       <c r="F58" s="7"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
+      <c r="D59" s="7">
+        <v>2</v>
+      </c>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
     </row>
     <row r="60" spans="2:6">
-      <c r="B60" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
+      <c r="B60" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
@@ -2853,52 +3176,46 @@
       <c r="F61" s="7"/>
     </row>
     <row r="62" spans="2:6">
-      <c r="B62" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="2:6">
-      <c r="B63" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="7" t="s">
-        <v>121</v>
-      </c>
+      <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
       <c r="F64" s="7"/>
     </row>
     <row r="65" spans="2:6">
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
     </row>
     <row r="66" spans="2:6">
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
     </row>
     <row r="67" spans="2:6">
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="14"/>
@@ -2941,27 +3258,6 @@
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
       <c r="F73" s="14"/>
-    </row>
-    <row r="74" spans="2:6">
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-    </row>
-    <row r="75" spans="2:6">
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-    </row>
-    <row r="76" spans="2:6">
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumu0\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4A8266-A835-456D-91AF-21BA11409AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C89CE42-2A95-4AB7-95ED-967D642BF768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="140">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -238,13 +238,6 @@
     <t>１日２コスト</t>
     <rPh sb="1" eb="2">
       <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実コスト</t>
-    <rPh sb="0" eb="1">
-      <t>ジツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1124,9 +1117,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1137,7 +1128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1179,10 +1170,13 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1556,13 +1550,13 @@
         <v>21</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -1570,7 +1564,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -1583,7 +1577,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="8"/>
     </row>
@@ -1593,7 +1587,7 @@
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D4" s="8"/>
     </row>
@@ -1608,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="13">
         <v>11</v>
@@ -1620,7 +1614,7 @@
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1633,17 +1627,17 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="8"/>
       <c r="G7" t="s">
         <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1656,7 +1650,7 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D8" s="8"/>
       <c r="N8" s="2"/>
@@ -1670,7 +1664,7 @@
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="8"/>
       <c r="N9" s="3"/>
@@ -1687,10 +1681,10 @@
         <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -1705,16 +1699,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -1730,11 +1724,11 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D12" s="8"/>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1750,11 +1744,11 @@
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="8"/>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -1770,7 +1764,7 @@
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" s="8"/>
       <c r="N14" s="3"/>
@@ -1787,7 +1781,7 @@
         <v>4</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -1800,7 +1794,7 @@
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D16" s="8"/>
       <c r="N16" s="2"/>
@@ -1814,7 +1808,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D17" s="8"/>
       <c r="N17" s="2"/>
@@ -1828,10 +1822,10 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1844,10 +1838,10 @@
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1875,7 +1869,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="13">
         <v>4</v>
@@ -1890,7 +1884,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8">
@@ -1906,7 +1900,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
@@ -1925,7 +1919,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="13">
         <v>11</v>
@@ -1944,7 +1938,7 @@
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D25" s="8"/>
       <c r="N25" s="1"/>
@@ -1958,10 +1952,10 @@
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1970,14 +1964,14 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1986,14 +1980,14 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2002,7 +1996,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8">
@@ -2021,7 +2015,7 @@
         <v>19</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="13">
         <v>34</v>
@@ -2036,16 +2030,16 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2054,14 +2048,14 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -2070,11 +2064,11 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D33" s="8"/>
       <c r="N33" s="1"/>
@@ -2084,13 +2078,13 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="8"/>
       <c r="N34" s="1"/>
@@ -2100,13 +2094,13 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="8"/>
       <c r="N35" s="2"/>
@@ -2116,13 +2110,13 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D36" s="13"/>
       <c r="N36" s="4"/>
@@ -2132,11 +2126,11 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="8"/>
       <c r="N37" s="2"/>
@@ -2146,10 +2140,10 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C38" s="13">
         <v>12</v>
@@ -2162,11 +2156,11 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D39" s="8"/>
       <c r="N39" s="2"/>
@@ -2176,11 +2170,11 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D40" s="8"/>
       <c r="N40" s="2"/>
@@ -2190,11 +2184,11 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D41" s="8"/>
       <c r="N41" s="1"/>
@@ -2204,11 +2198,11 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="8"/>
       <c r="N42" s="1"/>
@@ -2218,13 +2212,13 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D43" s="13"/>
       <c r="N43" s="1"/>
@@ -2234,13 +2228,13 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D44" s="13"/>
       <c r="N44" s="1"/>
@@ -2253,10 +2247,10 @@
         <v>3</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45" s="13"/>
       <c r="N45" s="1"/>
@@ -2426,27 +2420,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E21B2F-17A7-4263-AC36-EBB7CC62FACB}">
-  <dimension ref="B2:N73"/>
+  <dimension ref="B2:M73"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="26.625" customWidth="1"/>
     <col min="3" max="3" width="14.375" customWidth="1"/>
     <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="11.75" customWidth="1"/>
-    <col min="7" max="7" width="23.375" customWidth="1"/>
-    <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="11.625" customWidth="1"/>
-    <col min="10" max="10" width="14.375" customWidth="1"/>
-    <col min="11" max="11" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="23.375" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14">
+    <row r="2" spans="2:13">
       <c r="B2" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>30</v>
@@ -2454,413 +2447,380 @@
       <c r="E2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="N2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14">
+      <c r="F2" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="G2" s="19"/>
+      <c r="M2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13">
       <c r="B3" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="N3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14">
+      <c r="M3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13">
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="N4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14">
+      <c r="M4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
       <c r="B5" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
       <c r="I5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" t="s">
-        <v>71</v>
-      </c>
-      <c r="N5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="2:14">
+        <v>70</v>
+      </c>
+      <c r="M5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
       <c r="B6" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="J6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" t="s">
-        <v>120</v>
-      </c>
-      <c r="N6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="2:14">
+        <v>119</v>
+      </c>
+      <c r="M6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
       <c r="B7" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="N7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="2:14">
+      <c r="M7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
       <c r="B8" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="N8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="2:14">
+      <c r="M8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
       <c r="B9" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9">
+      <c r="H9" t="s">
         <v>40</v>
       </c>
-      <c r="N9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14">
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="M9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
       <c r="B10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10">
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="2:14">
+    <row r="11" spans="2:13">
       <c r="B11" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="I11" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14">
+      <c r="H11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
       <c r="B12" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="9">
         <v>18</v>
       </c>
       <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12">
+      <c r="F12" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="2:14">
-      <c r="B13" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18">
+    <row r="13" spans="2:13">
+      <c r="B13" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17">
         <v>12</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-    </row>
-    <row r="14" spans="2:14">
+      <c r="E13" s="17"/>
+    </row>
+    <row r="14" spans="2:13">
       <c r="B14" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7">
         <v>2</v>
       </c>
       <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="2:14">
+    </row>
+    <row r="15" spans="2:13">
       <c r="B15" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7">
         <v>4</v>
       </c>
       <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="2:14">
+    </row>
+    <row r="16" spans="2:13">
       <c r="B16" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
         <v>4</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="N16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
+      <c r="M16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7">
         <v>6</v>
       </c>
       <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="N17" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
-      <c r="B18" s="18" t="s">
-        <v>139</v>
+      <c r="M17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="17" t="s">
+        <v>138</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7">
         <v>2</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="N18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
-      <c r="B19" s="18" t="s">
-        <v>90</v>
+      <c r="M18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7">
         <v>2</v>
       </c>
       <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="2:14">
-      <c r="B20" s="18" t="s">
-        <v>91</v>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7">
         <v>2</v>
       </c>
       <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" spans="2:14">
+    </row>
+    <row r="21" spans="2:13">
       <c r="B21" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D21" s="9">
         <v>51</v>
       </c>
       <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-    </row>
-    <row r="22" spans="2:14">
+    </row>
+    <row r="22" spans="2:13">
       <c r="B22" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7">
         <v>10</v>
       </c>
       <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="2:14">
+    </row>
+    <row r="23" spans="2:13">
       <c r="B23" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7">
         <v>10</v>
       </c>
       <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="2:14">
+    </row>
+    <row r="24" spans="2:13">
       <c r="B24" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7">
         <v>20</v>
       </c>
       <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="2:14">
+    </row>
+    <row r="25" spans="2:13">
       <c r="B25" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7">
         <v>2</v>
       </c>
       <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="2:14">
+    </row>
+    <row r="26" spans="2:13">
       <c r="B26" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7">
         <v>5</v>
       </c>
       <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="2:14">
+    </row>
+    <row r="27" spans="2:13">
       <c r="B27" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7">
         <v>2</v>
       </c>
       <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="2:14">
+    </row>
+    <row r="28" spans="2:13">
       <c r="B28" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7">
         <v>2</v>
       </c>
       <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="2:14">
+    </row>
+    <row r="29" spans="2:13">
       <c r="B29" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="2:14">
+    </row>
+    <row r="30" spans="2:13">
       <c r="B30" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="2:14">
+    </row>
+    <row r="31" spans="2:13">
       <c r="B31" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="2:14">
+    </row>
+    <row r="32" spans="2:13">
       <c r="B32" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D33" s="18">
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="17">
         <v>6</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="E33" s="17"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="7" t="s">
         <v>20</v>
       </c>
@@ -2869,395 +2829,355 @@
         <v>4</v>
       </c>
       <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+      <c r="F34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
       <c r="B35" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7">
         <v>2</v>
       </c>
       <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="18" t="s">
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17">
+        <v>20</v>
+      </c>
+      <c r="E36" s="17"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18">
-        <v>20</v>
-      </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="7" t="s">
-        <v>107</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7">
         <v>2</v>
       </c>
       <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="2:7">
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7">
         <v>5</v>
       </c>
       <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="2:7">
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7">
         <v>5</v>
       </c>
       <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="2:7">
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7">
         <v>5</v>
       </c>
       <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="2:7">
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7">
         <v>1</v>
       </c>
       <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="2:7">
+    </row>
+    <row r="42" spans="2:6">
       <c r="B42" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7">
         <v>2</v>
       </c>
       <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="18">
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" s="17">
         <v>18</v>
       </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="E43" s="17"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7">
         <v>4</v>
       </c>
       <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="2:7">
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7">
         <v>4</v>
       </c>
       <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="2:7">
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7">
         <v>4</v>
       </c>
       <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="2:7">
+    </row>
+    <row r="47" spans="2:6">
       <c r="B47" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7">
         <v>4</v>
       </c>
       <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="2:7">
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7">
         <v>1</v>
       </c>
       <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="2:6">
+    </row>
+    <row r="49" spans="2:5">
       <c r="B49" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7">
         <v>1</v>
       </c>
       <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D50" s="18">
+    </row>
+    <row r="50" spans="2:5">
+      <c r="B50" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D50" s="17">
         <v>18</v>
       </c>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="E50" s="17"/>
+    </row>
+    <row r="51" spans="2:5">
       <c r="B51" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7">
         <v>4</v>
       </c>
       <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="2:6">
+    </row>
+    <row r="52" spans="2:5">
       <c r="B52" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7">
         <v>4</v>
       </c>
       <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-    </row>
-    <row r="53" spans="2:6">
+    </row>
+    <row r="53" spans="2:5">
       <c r="B53" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7">
         <v>4</v>
       </c>
       <c r="E53" s="7"/>
-      <c r="F53" s="7"/>
-    </row>
-    <row r="54" spans="2:6">
+    </row>
+    <row r="54" spans="2:5">
       <c r="B54" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7">
         <v>4</v>
       </c>
       <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-    </row>
-    <row r="55" spans="2:6">
+    </row>
+    <row r="55" spans="2:5">
       <c r="B55" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7">
         <v>1</v>
       </c>
       <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-    </row>
-    <row r="56" spans="2:6">
+    </row>
+    <row r="56" spans="2:5">
       <c r="B56" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7">
         <v>1</v>
       </c>
       <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-    </row>
-    <row r="57" spans="2:6">
+    </row>
+    <row r="57" spans="2:5">
       <c r="B57" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D57" s="9">
         <v>5</v>
       </c>
       <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-    </row>
-    <row r="58" spans="2:6">
+    </row>
+    <row r="58" spans="2:5">
       <c r="B58" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7">
         <v>2</v>
       </c>
       <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-    </row>
-    <row r="59" spans="2:6">
+    </row>
+    <row r="59" spans="2:5">
       <c r="B59" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7">
         <v>2</v>
       </c>
       <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-    </row>
-    <row r="60" spans="2:6">
+    </row>
+    <row r="60" spans="2:5">
       <c r="B60" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" s="13"/>
       <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-    </row>
-    <row r="61" spans="2:6">
+    </row>
+    <row r="61" spans="2:5">
       <c r="B61" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-    </row>
-    <row r="62" spans="2:6">
+    </row>
+    <row r="62" spans="2:5">
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
-    </row>
-    <row r="63" spans="2:6">
+    </row>
+    <row r="63" spans="2:5">
       <c r="B63" s="7"/>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-    </row>
-    <row r="64" spans="2:6">
+    </row>
+    <row r="64" spans="2:5">
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-    </row>
-    <row r="65" spans="2:6">
+    </row>
+    <row r="65" spans="2:5">
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
       <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-    </row>
-    <row r="66" spans="2:6">
+    </row>
+    <row r="66" spans="2:5">
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
       <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-    </row>
-    <row r="67" spans="2:6">
+    </row>
+    <row r="67" spans="2:5">
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
       <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-    </row>
-    <row r="68" spans="2:6">
+    </row>
+    <row r="68" spans="2:5">
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
       <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-    </row>
-    <row r="69" spans="2:6">
+    </row>
+    <row r="69" spans="2:5">
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
       <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-    </row>
-    <row r="70" spans="2:6">
+    </row>
+    <row r="70" spans="2:5">
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
       <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-    </row>
-    <row r="71" spans="2:6">
+    </row>
+    <row r="71" spans="2:5">
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
       <c r="D71" s="14"/>
       <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-    </row>
-    <row r="72" spans="2:6">
+    </row>
+    <row r="72" spans="2:5">
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
       <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-    </row>
-    <row r="73" spans="2:6">
+    </row>
+    <row r="73" spans="2:5">
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
       <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3276,30 +3196,30 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>55</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>56</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>57</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>58</v>
-      </c>
-      <c r="H2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3321,7 +3241,7 @@
       <c r="H4" s="15"/>
       <c r="J4" s="6"/>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3353,7 +3273,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" s="15">
         <v>31</v>
@@ -3405,7 +3325,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumu0\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C89CE42-2A95-4AB7-95ED-967D642BF768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6655B8F9-59C1-47D7-99FC-D933B3068F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -1128,7 +1128,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1173,10 +1173,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2450,7 +2447,6 @@
       <c r="F2" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="19"/>
       <c r="M2" t="s">
         <v>120</v>
       </c>
@@ -2462,7 +2458,9 @@
       <c r="C3" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="13"/>
+      <c r="D3" s="13">
+        <v>16</v>
+      </c>
       <c r="E3" s="13"/>
       <c r="M3" t="s">
         <v>121</v>
@@ -2473,7 +2471,9 @@
         <v>80</v>
       </c>
       <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
       <c r="E4" s="7"/>
       <c r="M4" t="s">
         <v>125</v>
@@ -2484,7 +2484,9 @@
         <v>79</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="7">
+        <v>2</v>
+      </c>
       <c r="E5" s="7"/>
       <c r="H5" t="s">
         <v>31</v>
@@ -2501,7 +2503,9 @@
         <v>81</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7">
+        <v>2</v>
+      </c>
       <c r="E6" s="7"/>
       <c r="H6" t="s">
         <v>32</v>
@@ -2521,7 +2525,9 @@
         <v>82</v>
       </c>
       <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
       <c r="E7" s="7"/>
       <c r="M7" t="s">
         <v>126</v>
@@ -2532,7 +2538,9 @@
         <v>83</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7">
+        <v>2</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="M8" t="s">
         <v>124</v>
@@ -2543,7 +2551,9 @@
         <v>84</v>
       </c>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
       <c r="E9" s="7"/>
       <c r="H9" t="s">
         <v>40</v>
@@ -2560,7 +2570,9 @@
         <v>83</v>
       </c>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7">
+        <v>2</v>
+      </c>
       <c r="E10" s="7"/>
       <c r="H10" t="s">
         <v>45</v>
@@ -2579,6 +2591,9 @@
       <c r="H11" t="s">
         <v>49</v>
       </c>
+      <c r="I11">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="9" t="s">
@@ -2779,7 +2794,9 @@
       <c r="C29" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="D29" s="9"/>
+      <c r="D29" s="9">
+        <v>16</v>
+      </c>
       <c r="E29" s="9"/>
     </row>
     <row r="30" spans="2:13">
@@ -2787,7 +2804,9 @@
         <v>100</v>
       </c>
       <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="D30" s="7">
+        <v>8</v>
+      </c>
       <c r="E30" s="7"/>
     </row>
     <row r="31" spans="2:13">
@@ -2795,7 +2814,9 @@
         <v>101</v>
       </c>
       <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
+      <c r="D31" s="7">
+        <v>8</v>
+      </c>
       <c r="E31" s="7"/>
     </row>
     <row r="32" spans="2:13">
@@ -3096,7 +3117,9 @@
       <c r="C60" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D60" s="13"/>
+      <c r="D60" s="13">
+        <v>4</v>
+      </c>
       <c r="E60" s="13"/>
     </row>
     <row r="61" spans="2:5">
@@ -3104,7 +3127,9 @@
         <v>118</v>
       </c>
       <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
+      <c r="D61" s="7">
+        <v>4</v>
+      </c>
       <c r="E61" s="7"/>
     </row>
     <row r="62" spans="2:5">

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6655B8F9-59C1-47D7-99FC-D933B3068F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D8B9B-5AD5-4717-B7DD-86DCF81D4529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -2459,7 +2459,7 @@
         <v>49</v>
       </c>
       <c r="D3" s="13">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E3" s="13"/>
       <c r="M3" t="s">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="7"/>
       <c r="M4" t="s">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7" s="7"/>
       <c r="M7" t="s">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E9" s="7"/>
       <c r="H9" t="s">
@@ -2592,7 +2592,7 @@
         <v>49</v>
       </c>
       <c r="I11">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="2:13">

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D8B9B-5AD5-4717-B7DD-86DCF81D4529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85569D19-FFCC-4FAA-8361-FC0DAFE7D2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="140">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2715,7 +2715,9 @@
       <c r="D21" s="9">
         <v>51</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E21" s="9">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="7" t="s">
@@ -2755,7 +2757,9 @@
       <c r="D25" s="7">
         <v>2</v>
       </c>
-      <c r="E25" s="7"/>
+      <c r="E25" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="7" t="s">
@@ -2765,7 +2769,9 @@
       <c r="D26" s="7">
         <v>5</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="7" t="s">
@@ -2785,7 +2791,9 @@
       <c r="D28" s="7">
         <v>2</v>
       </c>
-      <c r="E28" s="7"/>
+      <c r="E28" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="9" t="s">

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85569D19-FFCC-4FAA-8361-FC0DAFE7D2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBA9463-249B-4101-BF4C-F0D29D0FFF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="140">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -2474,7 +2474,9 @@
       <c r="D4" s="7">
         <v>6</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="M4" t="s">
         <v>125</v>
       </c>
@@ -2487,7 +2489,9 @@
       <c r="D5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="7" t="s">
+        <v>74</v>
+      </c>
       <c r="H5" t="s">
         <v>31</v>
       </c>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85569D19-FFCC-4FAA-8361-FC0DAFE7D2DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE579B1-E0C1-4CF1-9E8C-CE8275F1C44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="142">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -973,6 +973,14 @@
   </si>
   <si>
     <t>26, 36</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータタイプ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1010,7 +1018,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1089,6 +1097,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1128,7 +1142,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1167,13 +1181,19 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2444,7 +2464,7 @@
       <c r="E2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>133</v>
       </c>
       <c r="M2" t="s">
@@ -2617,14 +2637,14 @@
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16">
         <v>12</v>
       </c>
-      <c r="E13" s="17"/>
+      <c r="E13" s="16"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="7" t="s">
@@ -2673,7 +2693,7 @@
       </c>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>138</v>
       </c>
       <c r="C18" s="7"/>
@@ -2686,7 +2706,7 @@
       </c>
     </row>
     <row r="19" spans="2:13">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>89</v>
       </c>
       <c r="C19" s="7"/>
@@ -2696,7 +2716,7 @@
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>90</v>
       </c>
       <c r="C20" s="7"/>
@@ -2838,16 +2858,16 @@
       <c r="E32" s="9"/>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="17" t="s">
+      <c r="C33" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="16">
         <v>6</v>
       </c>
-      <c r="E33" s="17"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="7" t="s">
@@ -2873,14 +2893,14 @@
       <c r="E35" s="7"/>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17">
+      <c r="C36" s="16"/>
+      <c r="D36" s="16">
         <v>20</v>
       </c>
-      <c r="E36" s="17"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="7" t="s">
@@ -2943,16 +2963,16 @@
       <c r="E42" s="7"/>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <v>18</v>
       </c>
-      <c r="E43" s="17"/>
+      <c r="E43" s="16"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="7" t="s">
@@ -3015,16 +3035,16 @@
       <c r="E49" s="7"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="16">
         <v>18</v>
       </c>
-      <c r="E50" s="17"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51" spans="2:5">
       <c r="B51" s="7" t="s">
@@ -3285,6 +3305,10 @@
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
+      <c r="J5" s="18"/>
+      <c r="K5" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" s="15"/>
@@ -3294,6 +3318,10 @@
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
+      <c r="J6" s="19"/>
+      <c r="K6" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="B7" s="15"/>
@@ -3303,6 +3331,7 @@
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
+      <c r="J7" s="20"/>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
@@ -3311,12 +3340,12 @@
       <c r="B8" s="15">
         <v>31</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="12">
         <v>1</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
     </row>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE579B1-E0C1-4CF1-9E8C-CE8275F1C44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2069E62C-498C-4F3A-B18C-7DAEA3E86EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
         <v>40</v>
       </c>
       <c r="H10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1728,7 +1728,7 @@
         <v>45</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2069E62C-498C-4F3A-B18C-7DAEA3E86EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE579B1-E0C1-4CF1-9E8C-CE8275F1C44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
         <v>40</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1728,7 +1728,7 @@
         <v>45</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumu0\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2069E62C-498C-4F3A-B18C-7DAEA3E86EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEEAF85-811C-4EBD-BA1B-49E6624FE2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="16305" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
     <sheet name="アルファ" sheetId="3" r:id="rId2"/>
-    <sheet name="予定" sheetId="2" r:id="rId3"/>
+    <sheet name="ベータ" sheetId="4" r:id="rId3"/>
+    <sheet name="予定" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="155">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -108,16 +109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>・近ザコ敵</t>
-    <rPh sb="1" eb="2">
-      <t>キン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>UI素材</t>
     <rPh sb="2" eb="4">
       <t>ソザイ</t>
@@ -972,15 +963,128 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>26, 36</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アルファタイプ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>ベータタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ノックバック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃を最も近い敵に向ける</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>チカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→押し戻し</t>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タンクザコ敵</t>
+    <rPh sb="5" eb="6">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→デッキの設置</t>
+    <rPh sb="5" eb="7">
+      <t>セッチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ドロー演出</t>
+    <rPh sb="4" eb="6">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カードデザイン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→星１カードのコーディング</t>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→カードのグループ分け</t>
+    <rPh sb="9" eb="10">
+      <t>ワ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→星2カード6枚のコーディング</t>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→星3カード3枚のコーディング</t>
+    <rPh sb="1" eb="2">
+      <t>ホシ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>マイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カード使用時演出</t>
+    <rPh sb="3" eb="5">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>エンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>?</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>35, 36</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1564,16 +1668,16 @@
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -1581,7 +1685,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="13">
         <v>1</v>
@@ -1594,7 +1698,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D3" s="8"/>
     </row>
@@ -1604,7 +1708,7 @@
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="8"/>
     </row>
@@ -1619,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="13">
         <v>11</v>
@@ -1628,10 +1732,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1640,21 +1744,21 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" s="8"/>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1667,7 +1771,7 @@
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D8" s="8"/>
       <c r="N8" s="2"/>
@@ -1677,11 +1781,11 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" s="8"/>
       <c r="N9" s="3"/>
@@ -1698,10 +1802,10 @@
         <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1716,16 +1820,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1741,11 +1845,11 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" s="8"/>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1757,15 +1861,15 @@
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" s="8"/>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13">
         <v>6</v>
@@ -1777,11 +1881,11 @@
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="8"/>
       <c r="N14" s="3"/>
@@ -1791,14 +1895,14 @@
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8">
         <v>4</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -1807,11 +1911,11 @@
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" s="8"/>
       <c r="N16" s="2"/>
@@ -1821,11 +1925,11 @@
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D17" s="8"/>
       <c r="N17" s="2"/>
@@ -1835,14 +1939,14 @@
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1851,14 +1955,14 @@
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -1867,7 +1971,7 @@
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -1883,10 +1987,10 @@
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C21" s="13">
         <v>4</v>
@@ -1901,7 +2005,7 @@
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8">
@@ -1917,7 +2021,7 @@
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
@@ -1936,7 +2040,7 @@
         <v>1</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="13">
         <v>11</v>
@@ -1951,11 +2055,11 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="8" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="8" t="s">
-        <v>74</v>
+      <c r="C25" s="8">
+        <v>3</v>
       </c>
       <c r="D25" s="8"/>
       <c r="N25" s="1"/>
@@ -1965,14 +2069,14 @@
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="8" t="s">
-        <v>74</v>
+      <c r="C26" s="8">
+        <v>3</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -1981,14 +2085,14 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="8" t="s">
-        <v>74</v>
+      <c r="C27" s="8">
+        <v>2</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -1997,14 +2101,14 @@
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="8"/>
-      <c r="C28" s="8" t="s">
-        <v>74</v>
+      <c r="C28" s="8">
+        <v>1</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2013,7 +2117,7 @@
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8">
@@ -2029,10 +2133,10 @@
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="13">
         <v>34</v>
@@ -2047,16 +2151,16 @@
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2065,14 +2169,14 @@
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -2081,11 +2185,11 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D33" s="8"/>
       <c r="N33" s="1"/>
@@ -2095,13 +2199,13 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D34" s="8"/>
       <c r="N34" s="1"/>
@@ -2111,13 +2215,13 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="8"/>
       <c r="N35" s="2"/>
@@ -2127,13 +2231,13 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D36" s="13"/>
       <c r="N36" s="4"/>
@@ -2143,11 +2247,11 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="8"/>
       <c r="N37" s="2"/>
@@ -2157,10 +2261,10 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C38" s="13">
         <v>12</v>
@@ -2173,11 +2277,11 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="8"/>
       <c r="N39" s="2"/>
@@ -2187,11 +2291,11 @@
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D40" s="8"/>
       <c r="N40" s="2"/>
@@ -2201,11 +2305,11 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="8"/>
       <c r="N41" s="1"/>
@@ -2215,11 +2319,11 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D42" s="8"/>
       <c r="N42" s="1"/>
@@ -2229,13 +2333,13 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D43" s="13"/>
       <c r="N43" s="1"/>
@@ -2245,13 +2349,13 @@
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D44" s="13"/>
       <c r="N44" s="1"/>
@@ -2264,10 +2368,10 @@
         <v>3</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D45" s="13"/>
       <c r="N45" s="1"/>
@@ -2302,7 +2406,7 @@
     </row>
     <row r="49" spans="1:17">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -2311,7 +2415,7 @@
     </row>
     <row r="50" spans="1:17">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -2320,7 +2424,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -2329,7 +2433,7 @@
     </row>
     <row r="52" spans="1:17">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -2338,7 +2442,7 @@
     </row>
     <row r="53" spans="1:17">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -2437,7 +2541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97E21B2F-17A7-4263-AC36-EBB7CC62FACB}">
-  <dimension ref="B2:M73"/>
+  <dimension ref="A2:M93"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="26.625" customWidth="1"/>
@@ -2453,42 +2557,42 @@
   <sheetData>
     <row r="2" spans="2:13">
       <c r="B2" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D3" s="13">
         <v>26</v>
       </c>
       <c r="E3" s="13"/>
       <c r="M3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7">
@@ -2496,12 +2600,12 @@
       </c>
       <c r="E4" s="7"/>
       <c r="M4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7">
@@ -2509,18 +2613,18 @@
       </c>
       <c r="E5" s="7"/>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7">
@@ -2528,21 +2632,21 @@
       </c>
       <c r="E6" s="7"/>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7">
@@ -2550,12 +2654,12 @@
       </c>
       <c r="E7" s="7"/>
       <c r="M7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7">
@@ -2563,12 +2667,12 @@
       </c>
       <c r="E8" s="7"/>
       <c r="M8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7">
@@ -2576,18 +2680,18 @@
       </c>
       <c r="E9" s="7"/>
       <c r="H9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9">
         <v>40</v>
       </c>
       <c r="M9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7">
@@ -2595,21 +2699,21 @@
       </c>
       <c r="E10" s="7"/>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I10">
-        <v>51</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I11">
         <v>48</v>
@@ -2617,28 +2721,28 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D12" s="9">
         <v>18</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16">
@@ -2648,7 +2752,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7">
@@ -2658,7 +2762,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7">
@@ -2668,7 +2772,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7">
@@ -2676,12 +2780,12 @@
       </c>
       <c r="E16" s="7"/>
       <c r="M16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="B17" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7">
@@ -2689,12 +2793,12 @@
       </c>
       <c r="E17" s="7"/>
       <c r="M17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="B18" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7">
@@ -2702,12 +2806,12 @@
       </c>
       <c r="E18" s="7"/>
       <c r="M18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="B19" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7">
@@ -2715,9 +2819,9 @@
       </c>
       <c r="E19" s="7"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="1:13">
       <c r="B20" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7">
@@ -2725,23 +2829,23 @@
       </c>
       <c r="E20" s="7"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="1:13">
       <c r="B21" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="9">
-        <v>51</v>
+        <v>53.5</v>
       </c>
       <c r="E21" s="9">
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="1:13">
       <c r="B22" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7">
@@ -2749,9 +2853,9 @@
       </c>
       <c r="E22" s="7"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="1:13">
       <c r="B23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7">
@@ -2759,9 +2863,9 @@
       </c>
       <c r="E23" s="7"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="1:13">
       <c r="B24" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="7">
@@ -2769,33 +2873,33 @@
       </c>
       <c r="E24" s="7"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="1:13">
       <c r="B25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7">
         <v>2</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="B26" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7">
         <v>5</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="B27" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7">
@@ -2803,88 +2907,82 @@
       </c>
       <c r="E27" s="7"/>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="1:13">
       <c r="B28" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7">
         <v>2</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="9">
-        <v>16</v>
-      </c>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" spans="2:13">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>142</v>
+      </c>
       <c r="B30" s="7" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="E30" s="7"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>142</v>
+      </c>
       <c r="B31" s="7" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E31" s="7"/>
     </row>
-    <row r="32" spans="2:13">
-      <c r="B32" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" s="9"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D33" s="16">
-        <v>6</v>
-      </c>
-      <c r="E33" s="16"/>
-    </row>
-    <row r="34" spans="2:6">
+    <row r="32" spans="1:13">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9">
+        <v>13</v>
+      </c>
+      <c r="E33" s="9"/>
+    </row>
+    <row r="34" spans="1:5">
       <c r="B34" s="7" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E34" s="7"/>
-      <c r="F34" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
+    </row>
+    <row r="35" spans="1:5">
       <c r="B35" s="7" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7">
@@ -2892,345 +2990,553 @@
       </c>
       <c r="E35" s="7"/>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16">
-        <v>20</v>
-      </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="37" spans="2:6">
+    <row r="36" spans="1:5">
+      <c r="B36" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7">
+        <v>3</v>
+      </c>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37" spans="1:5">
       <c r="B37" s="7" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E37" s="7"/>
     </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="7" t="s">
-        <v>107</v>
-      </c>
+    <row r="38" spans="1:5">
+      <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="7">
-        <v>5</v>
-      </c>
+      <c r="D38" s="7"/>
       <c r="E38" s="7"/>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="7" t="s">
-        <v>108</v>
-      </c>
+    <row r="39" spans="1:5">
+      <c r="B39" s="7"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="7">
-        <v>5</v>
-      </c>
+      <c r="D39" s="7"/>
       <c r="E39" s="7"/>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7">
-        <v>5</v>
-      </c>
-      <c r="E40" s="7"/>
-    </row>
-    <row r="41" spans="2:6">
+    <row r="40" spans="1:5">
+      <c r="B40" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D40" s="9">
+        <v>16</v>
+      </c>
+      <c r="E40" s="9"/>
+    </row>
+    <row r="41" spans="1:5">
       <c r="B41" s="7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E41" s="7"/>
     </row>
-    <row r="42" spans="2:6">
+    <row r="42" spans="1:5">
       <c r="B42" s="7" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E42" s="7"/>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C43" s="16" t="s">
+    <row r="43" spans="1:5">
+      <c r="B43" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" s="9"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="16">
-        <v>18</v>
-      </c>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7">
+      <c r="D44" s="16">
         <v>4</v>
       </c>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="2:6">
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:5">
       <c r="B45" s="7" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="C45" s="7"/>
-      <c r="D45" s="7">
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="B46" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="B47" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="B48" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="B49" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D49" s="16">
+        <v>11</v>
+      </c>
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="B50" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7">
         <v>4</v>
       </c>
-      <c r="E45" s="7"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7">
-        <v>4</v>
-      </c>
-      <c r="E46" s="7"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7">
-        <v>4</v>
-      </c>
-      <c r="E47" s="7"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7">
-        <v>1</v>
-      </c>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7">
-        <v>1</v>
-      </c>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D50" s="16">
-        <v>18</v>
-      </c>
-      <c r="E50" s="16"/>
-    </row>
-    <row r="51" spans="2:5">
+      <c r="E50" s="7"/>
+      <c r="F50" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="B51" s="7" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E51" s="7"/>
     </row>
-    <row r="52" spans="2:5">
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>142</v>
+      </c>
       <c r="B52" s="7" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="7"/>
     </row>
-    <row r="53" spans="2:5">
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
       <c r="B53" s="7" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" s="7"/>
     </row>
-    <row r="54" spans="2:5">
-      <c r="B54" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7">
-        <v>4</v>
-      </c>
-      <c r="E54" s="7"/>
-    </row>
-    <row r="55" spans="2:5">
+    <row r="54" spans="1:6">
+      <c r="B54" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16">
+        <v>20</v>
+      </c>
+      <c r="E54" s="16"/>
+    </row>
+    <row r="55" spans="1:6">
       <c r="B55" s="7" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="7"/>
     </row>
-    <row r="56" spans="2:5">
+    <row r="56" spans="1:6">
       <c r="B56" s="7" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E56" s="7"/>
     </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D57" s="9">
+    <row r="57" spans="1:6">
+      <c r="B57" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7">
         <v>5</v>
       </c>
-      <c r="E57" s="9"/>
-    </row>
-    <row r="58" spans="2:5">
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" spans="1:6">
       <c r="B58" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E58" s="7"/>
     </row>
-    <row r="59" spans="2:5">
+    <row r="59" spans="1:6">
       <c r="B59" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7">
+        <v>1</v>
+      </c>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="B60" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7">
         <v>2</v>
       </c>
-      <c r="E59" s="7"/>
-    </row>
-    <row r="60" spans="2:5">
-      <c r="B60" s="13" t="s">
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="B61" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="16">
+        <v>18</v>
+      </c>
+      <c r="E61" s="16"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="B62" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7">
+        <v>4</v>
+      </c>
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="B63" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7">
+        <v>4</v>
+      </c>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="B64" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7">
+        <v>4</v>
+      </c>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="B65" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7">
+        <v>4</v>
+      </c>
+      <c r="E65" s="7"/>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="B66" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="B67" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7">
+        <v>1</v>
+      </c>
+      <c r="E67" s="7"/>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="B68" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" s="16">
+        <v>18</v>
+      </c>
+      <c r="E68" s="16"/>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="B69" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7">
+        <v>4</v>
+      </c>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="B70" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7">
+        <v>4</v>
+      </c>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="B71" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7">
+        <v>4</v>
+      </c>
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="B72" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7">
+        <v>4</v>
+      </c>
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="B73" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="B74" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="B75" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D75" s="9">
+        <v>5</v>
+      </c>
+      <c r="E75" s="9"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="B76" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7">
+        <v>2</v>
+      </c>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="B77" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7">
+        <v>2</v>
+      </c>
+      <c r="E77" s="7"/>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>142</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7">
+        <v>8</v>
+      </c>
+      <c r="E78" s="7"/>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="B80" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="13">
+        <v>4</v>
+      </c>
+      <c r="E80" s="13"/>
+    </row>
+    <row r="81" spans="2:5">
+      <c r="B81" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="13">
+      <c r="C81" s="7"/>
+      <c r="D81" s="7">
         <v>4</v>
       </c>
-      <c r="E60" s="13"/>
-    </row>
-    <row r="61" spans="2:5">
-      <c r="B61" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7">
-        <v>4</v>
-      </c>
-      <c r="E61" s="7"/>
-    </row>
-    <row r="62" spans="2:5">
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-    </row>
-    <row r="63" spans="2:5">
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-    </row>
-    <row r="64" spans="2:5">
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-    </row>
-    <row r="65" spans="2:5">
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-    </row>
-    <row r="66" spans="2:5">
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-    </row>
-    <row r="67" spans="2:5">
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-    </row>
-    <row r="68" spans="2:5">
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-    </row>
-    <row r="69" spans="2:5">
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-    </row>
-    <row r="70" spans="2:5">
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-    </row>
-    <row r="71" spans="2:5">
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-    </row>
-    <row r="72" spans="2:5">
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-    </row>
-    <row r="73" spans="2:5">
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
+      <c r="E81" s="7"/>
+    </row>
+    <row r="82" spans="2:5">
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+    </row>
+    <row r="83" spans="2:5">
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+    </row>
+    <row r="84" spans="2:5">
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+    </row>
+    <row r="85" spans="2:5">
+      <c r="B85" s="14"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="14"/>
+    </row>
+    <row r="86" spans="2:5">
+      <c r="B86" s="14"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="14"/>
+    </row>
+    <row r="87" spans="2:5">
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+    </row>
+    <row r="88" spans="2:5">
+      <c r="B88" s="14"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+    </row>
+    <row r="89" spans="2:5">
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="14"/>
+    </row>
+    <row r="90" spans="2:5">
+      <c r="B90" s="14"/>
+      <c r="C90" s="14"/>
+      <c r="D90" s="14"/>
+      <c r="E90" s="14"/>
+    </row>
+    <row r="91" spans="2:5">
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+    </row>
+    <row r="92" spans="2:5">
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+    </row>
+    <row r="93" spans="2:5">
+      <c r="B93" s="14"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3239,6 +3545,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9BC17E-E353-4357-8469-65D7808A19D3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{355F62B9-6B67-4B91-8209-BA5968FF032E}">
   <dimension ref="A2:K19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
@@ -3249,30 +3565,30 @@
   <sheetData>
     <row r="2" spans="1:11">
       <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>54</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>55</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>56</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>57</v>
-      </c>
-      <c r="H2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3294,7 +3610,7 @@
       <c r="H4" s="15"/>
       <c r="J4" s="6"/>
       <c r="K4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3307,7 +3623,7 @@
       <c r="H5" s="15"/>
       <c r="J5" s="18"/>
       <c r="K5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3320,7 +3636,7 @@
       <c r="H6" s="15"/>
       <c r="J6" s="19"/>
       <c r="K6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3335,7 +3651,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="15">
         <v>31</v>
@@ -3387,7 +3703,7 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>

--- a/DAT_cost.xlsx
+++ b/DAT_cost.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tumu0\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEEAF85-811C-4EBD-BA1B-49E6624FE2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79E6D2B5-C1BA-479C-A193-BBFE9CD17578}"/>
   </bookViews>
   <sheets>
     <sheet name="プロトタイプ" sheetId="1" r:id="rId1"/>
